--- a/hiring_companies_2026-10-28.xlsx
+++ b/hiring_companies_2026-10-28.xlsx
@@ -477,7 +477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Princeton Theological Seminary</t>
+          <t>Abuse Refuge Org</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,22 +492,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Communications and Content Manager</t>
+          <t>Journalist (Volunteer/Remote)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3957591782268674954</t>
+          <t>https://jooble.org/jdp/-2968540871672086909</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Princeton+Theological+Seminary</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Abuse+Refuge+Org</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lemon.io</t>
+          <t>Arroyo Seco Saints Baseball Club, Inc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Remote (Worldwide)</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Head of Engineering</t>
+          <t>Team Videographer/Video Editor Intern (California Collegiate League)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/software-development/head-of-engineering-2091134</t>
+          <t>https://jooble.org/jdp/3699986970539311465</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Lemon.io</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Arroyo+Seco+Saints+Baseball+Club%2C+Inc</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -564,14 +564,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>job link live</t>
+          <t>job link unknown</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OnePoint BFG Wealth Partners</t>
+          <t>Wow Remote Teams</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -586,22 +586,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Content and Thought Leadership Manager</t>
+          <t>Video Editor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-3205907868256086091</t>
+          <t>https://jooble.org/jdp/-7205683975652214779</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=OnePoint+BFG+Wealth+Partners</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Wow+Remote+Teams</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Glitterville Studios</t>
+          <t>LA 411</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -633,22 +633,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Social Media Manager</t>
+          <t>Assistant Video Editor</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-79166344238667645</t>
+          <t>https://jooble.org/jdp/3756640223480826919</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Glitterville+Studios</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=LA+411</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Eliassen Group</t>
+          <t>Fox Service Company</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -680,22 +680,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (TypeScript/Java/AI) | Java Developer | Paid Social Manager | Sr Platform Engineer I</t>
+          <t>News Reporter</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-6088744182752996325</t>
+          <t>https://jooble.org/jdp/-7010131595573719916</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Eliassen+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Fox+Service+Company</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Digital Admits</t>
+          <t>Bask and Lather Co</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -727,22 +727,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Digital Marketing Sales Manager</t>
+          <t>Social Media Coordinator</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-641485864113001200</t>
+          <t>https://jooble.org/jdp/-6462623426065914167</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Digital+Admits</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Bask+and+Lather+Co</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -759,12 +759,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Crestpoint Technology</t>
+          <t>Better Collective</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -774,22 +774,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer - Job Support</t>
+          <t>Social Media Intern</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2328126731744797347</t>
+          <t>https://jooble.org/jdp/9071090858474917108</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Crestpoint+Technology</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Better+Collective</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -806,12 +806,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Conexess Group</t>
+          <t>Catface</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lead Software Engineer (Platform Services) - Remote, United States</t>
+          <t>Contract Commercial Video &amp; Photo Editor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6210901252890182691</t>
+          <t>https://jooble.org/jdp/1618637803729146720</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Conexess+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Catface</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -853,12 +853,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Iris Software Inc.</t>
+          <t>Nexstar Broadcasting</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -868,22 +868,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lead Full Stack Python Developer ( 100 % Remote )</t>
+          <t>Talk and Entertainment Show Intern 2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4764991917714271274</t>
+          <t>https://jooble.org/jdp/-1851894929627524733</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Iris+Software+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Nexstar+Broadcasting</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Globe Life American Income Division: Surace Smith &amp; Partners...</t>
+          <t>Kindwell Partners</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -915,22 +915,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Remote Sales Representative</t>
+          <t>Social Media &amp; Content Manager (Part-Time)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3826553851734784191</t>
+          <t>https://jooble.org/jdp/556900011190825224</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Globe+Life+American+Income+Division%3A+Surace+Smith+%26+Partners...</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Kindwell+Partners</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXIT 4 SME Inc.</t>
+          <t>BairesDev</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -962,22 +962,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sales Representative - Remote</t>
+          <t>Social Media Manager - Remote Work</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5638400765156161632</t>
+          <t>https://jooble.org/jdp/-4045096823341566460</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=EXIT+4+SME+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=BairesDev</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -994,7 +994,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Veracity Ventures Inc.</t>
+          <t>New York Cloud Apps</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1009,22 +1009,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Territory Sales Representative</t>
+          <t>Remote Social Media Manager</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/589972792167318424</t>
+          <t>https://jooble.org/jdp/5711771459188009799</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Veracity+Ventures+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=New+York+Cloud+Apps</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TaxRise</t>
+          <t>Scale Marketing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1056,22 +1056,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Remote Sales Representative (FL)</t>
+          <t>Director of Marketing</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/720531148880997316</t>
+          <t>https://jooble.org/jdp/3123979714670684309</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=TaxRise</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Scale+Marketing</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1088,12 +1088,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Niche</t>
+          <t>Custom Ink</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1103,22 +1103,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Marketing Analyst (remote)</t>
+          <t>CRM Marketing Coordinator</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1931446102526892254</t>
+          <t>https://jooble.org/jdp/-1026404679515241277</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Niche</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Custom+Ink</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1135,12 +1135,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fuze Health</t>
+          <t>Versa Marketing Inc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer- Platform</t>
+          <t>Affiliate Marketing Manager</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3658549322513172496</t>
+          <t>https://jooble.org/jdp/6545727906875054835</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Fuze+Health</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Versa+Marketing+Inc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Essential Oxygen</t>
+          <t>Prequel Solutions</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Senior Manager, Creative Marketing Management</t>
+          <t>Senior Marketing Analytics Specialist</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-3202034553981401162</t>
+          <t>https://jooble.org/jdp/143805822354314402</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Essential+Oxygen</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Prequel+Solutions</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>Market My Market</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,22 +1244,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Manager, Cloud Platform Engineering | Principal, Cloud Platform Engineering</t>
+          <t>Digital PR Contractor</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/7353167469173661932</t>
+          <t>https://jooble.org/jdp/5871822364714513687</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Centene+Corporation</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Market+My+Market</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1276,12 +1276,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Forbes</t>
+          <t>Oceans</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1291,22 +1291,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Social Media Producer (Temporary)</t>
+          <t>Digital Marketing Manager</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2289017450375948953</t>
+          <t>https://jooble.org/jdp/2563917692757338533</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Forbes</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Oceans</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1323,7 +1323,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Marchay</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Senior Oracle Apps Developer</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1269324941511951048</t>
+          <t>https://jooble.org/jdp/3827685462904023187</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=General+Dynamics+Information+Technology</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Marchay</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Staples Inc.</t>
+          <t>Big Leap</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1385,22 +1385,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Territory Sales Representative - Commercial | Territory Sales Representative SLED - Maryland/DC</t>
+          <t>Community Director (Project Management)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1446188157868884752</t>
+          <t>https://jooble.org/jdp/-5462624860174305515</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Staples+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Big+Leap</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Arrow Electronics</t>
+          <t>Keenfinity</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1432,22 +1432,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Marketing Manager - Platform</t>
+          <t>Technical Solutions Engineer</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7833856323920728063</t>
+          <t>https://jooble.org/jdp/-5513859433547891807</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Arrow+Electronics</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Keenfinity</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1464,12 +1464,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SHI International Corp.</t>
+          <t>University of California, Santa Barbara</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1479,22 +1479,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Presales Solutions Engineer - Cloud Security | Presales Solutions Engineer - Network</t>
+          <t>Marketing Director</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/699952003932436835</t>
+          <t>https://jooble.org/jdp/7665870002788614617</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=SHI+International+Corp.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=University+of+California%2C+Santa+Barbara</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MOMIVATE</t>
+          <t>HopSkipDrive</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1526,22 +1526,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Video Editor</t>
+          <t>Engineering Manager, Platform &amp; DevOps</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-3639994650816457754</t>
+          <t>https://jooble.org/jdp/-73029295144856311</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=MOMIVATE</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=HopSkipDrive</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1558,7 +1558,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NTT DATA, Inc.</t>
+          <t>Happy Returns LLC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1573,22 +1573,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DB2 for z/OS Systems Programmer | IBMz Network Engineer | Implementation Manager - Mainframe Product Migration | Principal Sales Lead - Application Services</t>
+          <t>Platform Software Engineer</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4968451854093945044</t>
+          <t>https://jooble.org/jdp/8014856136721122140</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=NTT+DATA%2C+Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Happy+Returns+LLC</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1605,12 +1605,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MediaNews</t>
+          <t>Deque Systems Inc</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1620,22 +1620,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Reporter</t>
+          <t>Senior Full Stack Java Engineer</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1680937019550908301</t>
+          <t>https://jooble.org/jdp/2110978410032493961</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=MediaNews</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Deque+Systems+Inc</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1652,12 +1652,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Milwaukee Journal Sentinel</t>
+          <t>KForce</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1667,22 +1667,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Local News Editor - Sarasota Tribune</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-757221576369289758</t>
+          <t>https://jooble.org/jdp/3235758433839083960</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Milwaukee+Journal+Sentinel</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=KForce</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LaSalle University</t>
+          <t>The Planet Group</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1714,22 +1714,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Videographer</t>
+          <t>C#.Net Application Developer</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6970641102532983917</t>
+          <t>https://jooble.org/jdp/1391137347527338306</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=LaSalle+University</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Planet+Group</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1746,12 +1746,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jobgether SRL</t>
+          <t>Ambry Genetics</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1761,22 +1761,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PPC Specialist</t>
+          <t>Senior Software Engineer (Platform Engineering)-Remote, USA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-153232453887154707</t>
+          <t>https://jooble.org/jdp/2728439220329509477</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jobgether+SRL</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ambry+Genetics</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1793,12 +1793,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Perplexity AI</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1808,22 +1808,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Web Designer</t>
+          <t>Full-Stack Linux Cyber Application Developer | Unity 3D Engineer, Senior</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2180896692470355487</t>
+          <t>https://jooble.org/jdp/7805988903945973153</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Perplexity+AI</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Booz+Allen+Hamilton</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1840,12 +1840,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LegalZoom.com</t>
+          <t>Bright Vision Technologies</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1855,22 +1855,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Senior Web Designer, Design Systems</t>
+          <t>Oracle Cloud Security Engineer</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7361459487033159238</t>
+          <t>https://jooble.org/jdp/-2979005127231069933</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=LegalZoom.com</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Bright+Vision+Technologies</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1887,12 +1887,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Destin Auto Center</t>
+          <t>Programmers.io</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1902,22 +1902,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Social Media Coordinator</t>
+          <t>C++ Storage Developer/C++ with Storage/Embedded Engineer/NVMe Storage Engineer/Embedded/Storage- Embedded engineer</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7877910381220553905</t>
+          <t>https://jooble.org/jdp/-9157911447203441642</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Destin+Auto+Center</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Programmers.io</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1934,12 +1934,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Neighborly</t>
+          <t>Sonsoft</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1949,22 +1949,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Local Performance Marketing Specialist</t>
+          <t>Ui Java Developer</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6585664851088034080</t>
+          <t>https://jooble.org/jdp/-1381785041197366834</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Neighborly</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Sonsoft</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1981,12 +1981,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Linkedin</t>
+          <t>NPAworldwide</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1996,22 +1996,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sr. Lifecycle Marketing Manager, LinkedIn Marketing Solutions</t>
+          <t>Lead UI Software Engineer</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8637539230360416381</t>
+          <t>https://jooble.org/jdp/1539869283684405114</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Linkedin</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=NPAworldwide</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2028,12 +2028,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2043,22 +2043,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sr. Director, Marketing- Defense</t>
+          <t>Software Engineer, Backend (Python/C++)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3978574778237405469</t>
+          <t>https://jooble.org/jdp/-8461200220455744444</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Blue+Yonder</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SpaceX</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Skool</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Director, Digital Marketing</t>
+          <t>Principal Software Engineer, Backend (Go)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/5000584246449315512</t>
+          <t>https://jooble.org/jdp/3773675104793882314</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Crocs</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Skool</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2122,12 +2122,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2137,22 +2137,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Java Developer - WebMethod Engineer</t>
+          <t>Junior/Mid Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-3035027614825755002</t>
+          <t>https://jooble.org/jdp/-524274243987601139</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Butler</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Black+Canyon+Consulting</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2169,12 +2169,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cadence Bank</t>
+          <t>WSS Associates</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2184,22 +2184,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Lead Mainframe Platform Engineer - CICS, MQ &amp; zCEE</t>
+          <t>Senior Backend Engineer (Python/FastAPI/GraphQL)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-9211875177194520512</t>
+          <t>https://jooble.org/jdp/6655865476582136115</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Cadence+Bank</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=WSS+Associates</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2216,12 +2216,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>MCI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2231,22 +2231,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Senior Mobile Cross Platform Engineer</t>
+          <t>Remote Inbound Sales Specialist</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1802976105738273272</t>
+          <t>https://jooble.org/jdp/-7242850582357614961</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Chime</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=MCI</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2263,12 +2263,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Hologic</t>
+          <t>The Hondo Rodeo Fest</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2278,22 +2278,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Medical Device Digital Project Engineer</t>
+          <t>Group Sales Representative</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3154306875329844457</t>
+          <t>https://jooble.org/jdp/-4874754381300020208</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hologic</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Hondo+Rodeo+Fest</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2310,12 +2310,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Stelvio Inc.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2325,22 +2325,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Fixed Annuity Associate Wholesaler</t>
+          <t>Inside Sales Representative</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4259158816575021402</t>
+          <t>https://jooble.org/jdp/-1223715670623902598</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Lincoln+Financial+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Stelvio+Inc.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2357,12 +2357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Blacksmith Agency</t>
+          <t>Centurion Financial</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UI/UX Web Designer | Web Design Systems Designer (Remote, Chihuahua)</t>
+          <t>Remote Sales Specialist</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8724047004998506897</t>
+          <t>https://jooble.org/jdp/-9064399974868931256</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Blacksmith+Agency</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Centurion+Financial</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2404,12 +2404,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AgileGrid Solutions</t>
+          <t>Globe Life American Income Division: Surace Smith Bendure Ha...</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Web Designer</t>
+          <t>Remote Sales Representative</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-6403784056840745022</t>
+          <t>https://jooble.org/jdp/-2677238356186396961</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=AgileGrid+Solutions</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Globe+Life+American+Income+Division%3A+Surace+Smith+Bendure+Ha...</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2451,12 +2451,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Designer Jobs</t>
+          <t>Renewal by Andersen Metro &amp; Midwest</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Senior Web Designer | Web Designer</t>
+          <t>Inside Sales Representative - New Jersey</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/1774011278452649205</t>
+          <t>https://jooble.org/jdp/-6427964986572968346</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Designer+Jobs</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Renewal+by+Andersen+Metro+%26+Midwest</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2498,12 +2498,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mars Men</t>
+          <t>ProSearch</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2513,22 +2513,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Senior Web Designer</t>
+          <t>Sales Engagement Specialist - Remote</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8459079837524676115</t>
+          <t>https://jooble.org/jdp/5483630948287254816</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Mars+Men</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ProSearch</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2545,12 +2545,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Etna Interactive</t>
+          <t>Roethlisberger Life Group</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2560,22 +2560,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Remote Senior Web Designer: UI/UX for Growth in Small Biz | Web Designer - (Remote)</t>
+          <t>Inside Sales Representative - Remote | Work From Home</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-762756309366577028</t>
+          <t>https://jooble.org/jdp/-4827646283669999627</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Etna+Interactive</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Roethlisberger+Life+Group</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2592,12 +2592,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AIOS (YC W20/S21)</t>
+          <t>LIX, Inc</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2607,22 +2607,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Conversion-Driven Web Designer | Fully Remote &amp; AI-Powered</t>
+          <t>Territory Sales Manager - East Coast</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-3327266457713529946</t>
+          <t>https://jooble.org/jdp/7918992163118458452</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=AIOS+%28YC+W20%2FS21%29</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=LIX%2C+Inc</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2639,12 +2639,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>WD.ai</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2654,22 +2654,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Web Brand Designer - Inventive, Accessible UX &amp; Systems</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8202652907704381449</t>
+          <t>https://jooble.org/jdp/-7690055940645289962</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Figma</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=WD.ai</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2686,12 +2686,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Rally.org</t>
+          <t>Arena</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2701,22 +2701,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Digital Web Designer</t>
+          <t>COMPETE Digital: Seasonal Web Graphic Designer | Human Age Digital: Graphic and Web Designer</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-8250338758759398830</t>
+          <t>https://jooble.org/jdp/1754578893664232303</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Rally.org</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Arena</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>The BMA Media Group</t>
+          <t>Treasurefy</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2748,22 +2748,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Web Designer</t>
+          <t>Remote Wix Web Designer Freelance to Full-Time | Wix Web Designers Needed at Awesome Growing Agency</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8899318524495729837</t>
+          <t>https://jooble.org/jdp/-121887145490554164</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+BMA+Media+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Treasurefy</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2780,12 +2780,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Hearst</t>
+          <t>Suncap Technology</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2795,22 +2795,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Features Multimedia Journalist (Los Angeles)</t>
+          <t>Web Content Designer IV / Remote , 6+ Months Contract</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3264797144653403482</t>
+          <t>https://jooble.org/jdp/-3870605048130362744</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hearst</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Suncap+Technology</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
